--- a/input/Studies/MEET2/CompOverload.xlsx
+++ b/input/Studies/MEET2/CompOverload.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\METEC\MAES2\input\Studies\MEET2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9961093D-F96F-4B2D-A644-7F53D43C77EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E68348-3B6C-4169-AB10-CD9671FF50E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="937" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25070" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="937" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Simulation Parameters" sheetId="1" r:id="rId1"/>
@@ -1481,7 +1481,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1489,7 +1489,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="12">
-        <v>1E-4</v>
+        <v>0.5</v>
       </c>
       <c r="M2" s="12">
         <v>5</v>
@@ -3544,7 +3544,7 @@
         <v>9</v>
       </c>
       <c r="O2" s="12">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="P2" t="s">
         <v>52</v>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="12">
-        <v>1E-4</v>
+        <v>0.5</v>
       </c>
       <c r="M3" s="12">
         <v>3</v>
@@ -3600,7 +3600,7 @@
         <v>7</v>
       </c>
       <c r="O3" s="12">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="P3" t="s">
         <v>70</v>
@@ -3977,7 +3977,7 @@
         <v>1E-10</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>42</v>

--- a/input/Studies/MEET2/CompOverload.xlsx
+++ b/input/Studies/MEET2/CompOverload.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\METEC\MAES2\input\Studies\MEET2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\METEC\MAES_dev\input\Studies\MEET2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9961093D-F96F-4B2D-A644-7F53D43C77EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70029030-0543-43F6-A690-7C823424E781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="937" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-20970" yWindow="1000" windowWidth="4080" windowHeight="11320" tabRatio="937" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Simulation Parameters" sheetId="1" r:id="rId1"/>
@@ -1481,7 +1481,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3535,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="L2" s="12">
-        <v>1E-4</v>
+        <v>0.5</v>
       </c>
       <c r="M2" s="12">
         <v>5</v>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="12">
-        <v>1E-4</v>
+        <v>0.5</v>
       </c>
       <c r="M3" s="12">
         <v>3</v>
@@ -4339,16 +4339,19 @@
         <v>2</v>
       </c>
       <c r="AA2" s="31">
-        <v>0.5</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="AB2" s="32">
-        <v>3000</v>
+        <f>3000+11000</f>
+        <v>14000</v>
       </c>
       <c r="AC2" s="32">
-        <v>6000</v>
+        <f>6000+11000</f>
+        <v>17000</v>
       </c>
       <c r="AD2" s="32">
-        <v>5000</v>
+        <f>5000+11000</f>
+        <v>16000</v>
       </c>
       <c r="AE2" s="50" t="b">
         <v>0</v>
@@ -4440,16 +4443,19 @@
         <v>2</v>
       </c>
       <c r="AA3" s="31">
-        <v>0.5</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="AB3" s="32">
-        <v>3000</v>
+        <f>AB2</f>
+        <v>14000</v>
       </c>
       <c r="AC3" s="32">
-        <v>6000</v>
+        <f>AC2</f>
+        <v>17000</v>
       </c>
       <c r="AD3" s="32">
-        <v>5000</v>
+        <f>AD2</f>
+        <v>16000</v>
       </c>
       <c r="AE3" s="50" t="b">
         <v>0</v>

--- a/input/Studies/MEET2/CompOverload.xlsx
+++ b/input/Studies/MEET2/CompOverload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\METEC\MAES_dev\input\Studies\MEET2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70029030-0543-43F6-A690-7C823424E781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CD426C-80A6-4A1B-AE8D-1A9F57BA835B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-20970" yWindow="1000" windowWidth="4080" windowHeight="11320" tabRatio="937" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="937" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Simulation Parameters" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,8 @@
     <sheet name="Separators" sheetId="5" r:id="rId6"/>
     <sheet name="Dehydrators" sheetId="28" r:id="rId7"/>
     <sheet name="Compressors" sheetId="27" r:id="rId8"/>
-    <sheet name="TankBattery" sheetId="23" r:id="rId9"/>
-    <sheet name="Flares" sheetId="24" r:id="rId10"/>
+    <sheet name="Flares" sheetId="24" r:id="rId9"/>
+    <sheet name="TankBattery" sheetId="23" r:id="rId10"/>
     <sheet name="Probes" sheetId="22" r:id="rId11"/>
     <sheet name="FFLinks (2)" sheetId="29" r:id="rId12"/>
     <sheet name="FFLinks" sheetId="16" r:id="rId13"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="242">
   <si>
     <t>Simulation Start Date</t>
   </si>
@@ -723,12 +723,6 @@
     <t>Actuator Type [Gas, Air, Electric, Mechanistic Gas]</t>
   </si>
   <si>
-    <t>PRV Threshold [scfh]</t>
-  </si>
-  <si>
-    <t>Max Downstream Equipment Capacity [scfh]</t>
-  </si>
-  <si>
     <t>Lean Glycol Circulation Rate [gal/min]</t>
   </si>
   <si>
@@ -741,9 +735,6 @@
     <t>Mechanistic Thief Hatch pLeak</t>
   </si>
   <si>
-    <t>Tank Inlet Flow at Max Downstream Equipment Capacity</t>
-  </si>
-  <si>
     <t>Tank Controlled [True, False]</t>
   </si>
   <si>
@@ -814,6 +805,9 @@
   </si>
   <si>
     <t>Probes</t>
+  </si>
+  <si>
+    <t>Overpressure Threshold [scfh]</t>
   </si>
 </sst>
 </file>
@@ -1506,135 +1500,319 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E495659F-EBB3-407C-AE55-FCBF01FB0933}">
-  <dimension ref="A1:S2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFAD4290-2460-4C37-84AA-1F2DBF51FDF7}">
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="16" width="14.28515625" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="63.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8" customWidth="1"/>
+    <col min="22" max="23" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" customWidth="1"/>
+    <col min="25" max="27" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" customWidth="1"/>
+    <col min="29" max="29" width="27" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="63.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" s="2" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="33" t="s">
-        <v>93</v>
-      </c>
-      <c r="G1" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="I1" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="N1" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="O1" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="P1" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q1" s="7" t="s">
+      <c r="J1" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="M1" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="N1" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="O1" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="P1" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q1" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="R1" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="S1" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="T1" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="U1" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="V1" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="W1" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="X1" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y1" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z1" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA1" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB1" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="AC1" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="6">
+        <v>2</v>
+      </c>
+      <c r="H2" s="6">
+        <v>365</v>
+      </c>
+      <c r="I2" s="6">
+        <v>4.3276E-3</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="29">
+        <v>0</v>
+      </c>
+      <c r="N2" s="29">
+        <v>365</v>
+      </c>
+      <c r="O2" s="29">
+        <v>0.34166999999999997</v>
+      </c>
+      <c r="P2" s="30">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="30">
+        <v>365</v>
+      </c>
+      <c r="R2" s="30">
+        <v>0.14960999999999999</v>
+      </c>
+      <c r="S2" s="29">
+        <v>3</v>
+      </c>
+      <c r="T2" s="29">
         <v>7</v>
       </c>
-      <c r="R1" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="S1" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" s="6">
+      <c r="U2" s="29">
+        <v>0.34166999999999997</v>
+      </c>
+      <c r="V2" s="30">
+        <v>7</v>
+      </c>
+      <c r="W2" s="30">
+        <v>7</v>
+      </c>
+      <c r="X2" s="30">
+        <v>0.14960999999999999</v>
+      </c>
+      <c r="Y2" s="31">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="31">
+        <v>2</v>
+      </c>
+      <c r="AA2" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="AB2" s="32">
+        <v>10000</v>
+      </c>
+      <c r="AC2" s="50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>140</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="6">
+        <v>2</v>
+      </c>
+      <c r="H3" s="6">
+        <v>365</v>
+      </c>
+      <c r="I3" s="6">
+        <v>4.3276E-3</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="29">
         <v>0</v>
       </c>
-      <c r="D2" s="6">
+      <c r="N3" s="29">
         <v>365</v>
       </c>
-      <c r="E2" s="6">
-        <v>1E-4</v>
-      </c>
-      <c r="F2" s="34">
-        <v>0.75</v>
-      </c>
-      <c r="G2" s="34">
+      <c r="O3" s="29">
+        <v>0.34166999999999997</v>
+      </c>
+      <c r="P3" s="30">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="30">
+        <v>365</v>
+      </c>
+      <c r="R3" s="30">
+        <v>0.14960999999999999</v>
+      </c>
+      <c r="S3" s="29">
+        <v>3</v>
+      </c>
+      <c r="T3" s="29">
+        <v>7</v>
+      </c>
+      <c r="U3" s="29">
+        <v>0.34166999999999997</v>
+      </c>
+      <c r="V3" s="30">
+        <v>7</v>
+      </c>
+      <c r="W3" s="30">
+        <v>7</v>
+      </c>
+      <c r="X3" s="30">
+        <v>0.14960999999999999</v>
+      </c>
+      <c r="Y3" s="31">
         <v>1</v>
       </c>
-      <c r="H2" s="34">
+      <c r="Z3" s="31">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="AB3" s="32">
+        <f>AB2</f>
+        <v>10000</v>
+      </c>
+      <c r="AC3" s="50" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="34">
-        <v>0.9</v>
-      </c>
-      <c r="J2" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="K2" s="12">
-        <v>2</v>
-      </c>
-      <c r="L2" s="12">
-        <v>2</v>
-      </c>
-      <c r="M2" s="12">
-        <v>0</v>
-      </c>
-      <c r="N2" s="19">
-        <v>10</v>
-      </c>
-      <c r="O2" s="19">
-        <v>10</v>
-      </c>
-      <c r="P2" s="19">
-        <v>0.98</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>105</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="AD3" t="s">
         <v>141</v>
       </c>
-      <c r="S2" t="s">
-        <v>144</v>
+      <c r="AE3" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -1668,7 +1846,7 @@
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -2491,13 +2669,13 @@
         <v>47</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>51</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -2631,10 +2809,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2663,10 +2841,10 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2855,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -3009,7 +3187,7 @@
         <v>106</v>
       </c>
       <c r="R2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="S2" t="s">
         <v>137</v>
@@ -3273,7 +3451,7 @@
         <v>106</v>
       </c>
       <c r="AK2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AL2" t="s">
         <v>137</v>
@@ -3409,7 +3587,7 @@
         <v>106</v>
       </c>
       <c r="Q2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="R2" t="s">
         <v>137</v>
@@ -3535,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="L2" s="12">
-        <v>0.5</v>
+        <v>0.999</v>
       </c>
       <c r="M2" s="12">
         <v>5</v>
       </c>
       <c r="N2" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" s="12">
         <v>0.6</v>
@@ -3591,13 +3769,13 @@
         <v>0</v>
       </c>
       <c r="L3" s="12">
-        <v>0.5</v>
+        <v>0.999</v>
       </c>
       <c r="M3" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N3" s="12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O3" s="12">
         <v>0.6</v>
@@ -3660,7 +3838,7 @@
         <v>198</v>
       </c>
       <c r="G1" s="45" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H1" s="45" t="s">
         <v>199</v>
@@ -3792,10 +3970,10 @@
         <v>8</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D1" s="52" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>40</v>
@@ -3810,7 +3988,7 @@
         <v>146</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J1" s="37" t="s">
         <v>147</v>
@@ -3870,10 +4048,10 @@
         <v>165</v>
       </c>
       <c r="AC1" s="41" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AD1" s="41" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AE1" s="41" t="s">
         <v>166</v>
@@ -3885,10 +4063,10 @@
         <v>168</v>
       </c>
       <c r="AH1" s="41" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AI1" s="18" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AJ1" s="41" t="s">
         <v>169</v>
@@ -3897,10 +4075,10 @@
         <v>170</v>
       </c>
       <c r="AL1" s="35" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AM1" s="35" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AN1" s="35" t="s">
         <v>171</v>
@@ -3909,10 +4087,10 @@
         <v>172</v>
       </c>
       <c r="AP1" s="41" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AQ1" s="41" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AR1" s="41" t="s">
         <v>173</v>
@@ -3921,10 +4099,10 @@
         <v>174</v>
       </c>
       <c r="AT1" s="42" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AU1" s="42" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AV1" s="42" t="s">
         <v>175</v>
@@ -3933,10 +4111,10 @@
         <v>176</v>
       </c>
       <c r="AX1" s="35" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AY1" s="35" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AZ1" s="35" t="s">
         <v>177</v>
@@ -3983,13 +4161,13 @@
         <v>42</v>
       </c>
       <c r="J2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K2">
         <v>0.7</v>
       </c>
       <c r="L2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M2">
         <v>0.35</v>
@@ -4134,337 +4312,135 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFAD4290-2460-4C37-84AA-1F2DBF51FDF7}">
-  <dimension ref="A1:AG3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E495659F-EBB3-407C-AE55-FCBF01FB0933}">
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
-    <col min="7" max="9" width="11.5703125" customWidth="1"/>
-    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" customWidth="1"/>
-    <col min="13" max="14" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="24" width="8" customWidth="1"/>
-    <col min="25" max="30" width="13" customWidth="1"/>
-    <col min="31" max="31" width="63.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="16" width="14.28515625" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="63.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="2" customFormat="1" ht="120" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="10" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="N1" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="O1" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="P1" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="R1" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="6">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6">
+        <v>365</v>
+      </c>
+      <c r="E2" s="6">
+        <v>1E-4</v>
+      </c>
+      <c r="F2" s="34">
+        <v>0.75</v>
+      </c>
+      <c r="G2" s="34">
+        <v>1</v>
+      </c>
+      <c r="H2" s="34">
+        <v>1</v>
+      </c>
+      <c r="I2" s="34">
+        <v>0.9</v>
+      </c>
+      <c r="J2" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="K2" s="12">
+        <v>2</v>
+      </c>
+      <c r="L2" s="12">
+        <v>2</v>
+      </c>
+      <c r="M2" s="12">
+        <v>0</v>
+      </c>
+      <c r="N2" s="19">
         <v>10</v>
       </c>
-      <c r="J1" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="K1" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="L1" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="M1" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="N1" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="O1" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="P1" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q1" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="R1" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="S1" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="T1" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="U1" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="V1" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="W1" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="X1" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="Y1" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="Z1" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA1" s="27" t="s">
-        <v>218</v>
-      </c>
-      <c r="AB1" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="AC1" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="AD1" s="27" t="s">
-        <v>214</v>
-      </c>
-      <c r="AE1" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="AF1" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="AG1" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="6">
-        <v>2</v>
-      </c>
-      <c r="H2" s="6">
-        <v>365</v>
-      </c>
-      <c r="I2" s="6">
-        <v>4.3276E-3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" s="29">
-        <v>0</v>
-      </c>
-      <c r="N2" s="29">
-        <v>365</v>
-      </c>
-      <c r="O2" s="29">
-        <v>0.34166999999999997</v>
-      </c>
-      <c r="P2" s="30">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="30">
-        <v>365</v>
-      </c>
-      <c r="R2" s="30">
-        <v>0.14960999999999999</v>
-      </c>
-      <c r="S2" s="29">
-        <v>3</v>
-      </c>
-      <c r="T2" s="29">
-        <v>7</v>
-      </c>
-      <c r="U2" s="29">
-        <v>0.34166999999999997</v>
-      </c>
-      <c r="V2" s="30">
-        <v>7</v>
-      </c>
-      <c r="W2" s="30">
-        <v>7</v>
-      </c>
-      <c r="X2" s="30">
-        <v>0.14960999999999999</v>
-      </c>
-      <c r="Y2" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="31">
-        <v>2</v>
-      </c>
-      <c r="AA2" s="31">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="AB2" s="32">
-        <f>3000+11000</f>
-        <v>14000</v>
-      </c>
-      <c r="AC2" s="32">
-        <f>6000+11000</f>
-        <v>17000</v>
-      </c>
-      <c r="AD2" s="32">
-        <f>5000+11000</f>
-        <v>16000</v>
-      </c>
-      <c r="AE2" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>140</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="6">
-        <v>2</v>
-      </c>
-      <c r="H3" s="6">
-        <v>365</v>
-      </c>
-      <c r="I3" s="6">
-        <v>4.3276E-3</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="29">
-        <v>0</v>
-      </c>
-      <c r="N3" s="29">
-        <v>365</v>
-      </c>
-      <c r="O3" s="29">
-        <v>0.34166999999999997</v>
-      </c>
-      <c r="P3" s="30">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="30">
-        <v>365</v>
-      </c>
-      <c r="R3" s="30">
-        <v>0.14960999999999999</v>
-      </c>
-      <c r="S3" s="29">
-        <v>3</v>
-      </c>
-      <c r="T3" s="29">
-        <v>7</v>
-      </c>
-      <c r="U3" s="29">
-        <v>0.34166999999999997</v>
-      </c>
-      <c r="V3" s="30">
-        <v>7</v>
-      </c>
-      <c r="W3" s="30">
-        <v>7</v>
-      </c>
-      <c r="X3" s="30">
-        <v>0.14960999999999999</v>
-      </c>
-      <c r="Y3" s="31">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="31">
-        <v>2</v>
-      </c>
-      <c r="AA3" s="31">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="AB3" s="32">
-        <f>AB2</f>
-        <v>14000</v>
-      </c>
-      <c r="AC3" s="32">
-        <f>AC2</f>
-        <v>17000</v>
-      </c>
-      <c r="AD3" s="32">
-        <f>AD2</f>
-        <v>16000</v>
-      </c>
-      <c r="AE3" s="50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
+      <c r="O2" s="19">
+        <v>10</v>
+      </c>
+      <c r="P2" s="19">
+        <v>0.98</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>105</v>
+      </c>
+      <c r="R2" t="s">
         <v>141</v>
       </c>
-      <c r="AG3" t="s">
-        <v>221</v>
+      <c r="S2" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/input/Studies/MEET2/CompOverload.xlsx
+++ b/input/Studies/MEET2/CompOverload.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\METEC\MAES_dev\input\Studies\MEET2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46CD426C-80A6-4A1B-AE8D-1A9F57BA835B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EDFCA7-863B-4C10-AD7F-D6A42648BD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="937" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25070" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="937" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global Simulation Parameters" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="243">
   <si>
     <t>Simulation Start Date</t>
   </si>
@@ -808,6 +808,9 @@
   </si>
   <si>
     <t>Overpressure Threshold [scfh]</t>
+  </si>
+  <si>
+    <t>Downstream Tank Mechanistic Flag</t>
   </si>
 </sst>
 </file>
@@ -3600,7 +3603,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -3609,20 +3612,21 @@
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.85546875" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" customWidth="1"/>
-    <col min="15" max="15" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="10" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" s="10" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
@@ -3641,44 +3645,47 @@
       <c r="F1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="K1" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="L1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="M1" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="N1" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="O1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="P1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="S1" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -3697,44 +3704,47 @@
       <c r="F2" s="6">
         <v>0.02</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>1</v>
       </c>
-      <c r="I2" s="16">
+      <c r="J2" s="16">
         <v>4</v>
       </c>
-      <c r="J2" s="16">
+      <c r="K2" s="16">
         <v>20</v>
       </c>
-      <c r="K2" s="12">
+      <c r="L2" s="12">
         <v>0</v>
       </c>
-      <c r="L2" s="12">
-        <v>0.999</v>
-      </c>
       <c r="M2" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="N2" s="12">
         <v>5</v>
       </c>
-      <c r="N2" s="12">
+      <c r="O2" s="12">
         <v>10</v>
       </c>
-      <c r="O2" s="12">
+      <c r="P2" s="12">
         <v>0.6</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>138</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -3753,40 +3763,43 @@
       <c r="F3" s="6">
         <v>0.02</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1</v>
       </c>
-      <c r="I3" s="16">
+      <c r="J3" s="16">
         <v>5</v>
       </c>
-      <c r="J3" s="16">
+      <c r="K3" s="16">
         <v>25</v>
       </c>
-      <c r="K3" s="12">
+      <c r="L3" s="12">
         <v>0</v>
       </c>
-      <c r="L3" s="12">
-        <v>0.999</v>
-      </c>
       <c r="M3" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="N3" s="12">
         <v>5</v>
       </c>
-      <c r="N3" s="12">
+      <c r="O3" s="12">
         <v>10</v>
       </c>
-      <c r="O3" s="12">
+      <c r="P3" s="12">
         <v>0.6</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>70</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>139</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>143</v>
       </c>
     </row>

--- a/input/Studies/MEET2/CompOverload.xlsx
+++ b/input/Studies/MEET2/CompOverload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\METEC\MAES_dev\input\Studies\MEET2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7EDFCA7-863B-4C10-AD7F-D6A42648BD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5935EEB-F64D-4A99-ABBE-5D9BFA2DC4A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25070" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="937" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="242">
   <si>
     <t>Simulation Start Date</t>
   </si>
@@ -726,15 +726,6 @@
     <t>Lean Glycol Circulation Rate [gal/min]</t>
   </si>
   <si>
-    <t>Mechanistic Thief Hatch Leak MTTR min [days]</t>
-  </si>
-  <si>
-    <t>Mechanistic Thief Hatch Leak MTTR max [days]</t>
-  </si>
-  <si>
-    <t>Mechanistic Thief Hatch pLeak</t>
-  </si>
-  <si>
     <t>Tank Controlled [True, False]</t>
   </si>
   <si>
@@ -810,7 +801,13 @@
     <t>Overpressure Threshold [scfh]</t>
   </si>
   <si>
-    <t>Downstream Tank Mechanistic Flag</t>
+    <t>Mechanisitic Overpressure Vent Leaks MTTR min [days]</t>
+  </si>
+  <si>
+    <t>Mechanisitic Overpressure Vent Leaks MTTR max [days]</t>
+  </si>
+  <si>
+    <t>Mechanisitic Overpressure Vent Leaks pLeak</t>
   </si>
 </sst>
 </file>
@@ -1525,7 +1522,9 @@
     <col min="21" max="21" width="8" customWidth="1"/>
     <col min="22" max="23" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="8" customWidth="1"/>
-    <col min="25" max="27" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.28515625" customWidth="1"/>
+    <col min="26" max="26" width="12.7109375" customWidth="1"/>
+    <col min="27" max="27" width="14" customWidth="1"/>
     <col min="28" max="28" width="14.7109375" customWidth="1"/>
     <col min="29" max="29" width="27" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="63.7109375" bestFit="1" customWidth="1"/>
@@ -1606,19 +1605,19 @@
         <v>193</v>
       </c>
       <c r="Y1" s="27" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z1" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="AA1" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="AB1" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="AC1" s="49" t="s">
         <v>214</v>
-      </c>
-      <c r="Z1" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA1" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="AB1" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="AC1" s="49" t="s">
-        <v>217</v>
       </c>
       <c r="AD1" s="7" t="s">
         <v>136</v>
@@ -1707,7 +1706,7 @@
         <v>2</v>
       </c>
       <c r="AA2" s="31">
-        <v>0.2</v>
+        <v>1E-4</v>
       </c>
       <c r="AB2" s="32">
         <v>10000</v>
@@ -1719,7 +1718,7 @@
         <v>140</v>
       </c>
       <c r="AE2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -1802,7 +1801,7 @@
         <v>2</v>
       </c>
       <c r="AA3" s="31">
-        <v>0.2</v>
+        <v>1E-4</v>
       </c>
       <c r="AB3" s="32">
         <f>AB2</f>
@@ -1815,7 +1814,7 @@
         <v>141</v>
       </c>
       <c r="AE3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -1849,7 +1848,7 @@
         <v>47</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -2672,13 +2671,13 @@
         <v>47</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>51</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -2812,10 +2811,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2844,10 +2843,10 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3036,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -3190,7 +3189,7 @@
         <v>106</v>
       </c>
       <c r="R2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="S2" t="s">
         <v>137</v>
@@ -3454,7 +3453,7 @@
         <v>106</v>
       </c>
       <c r="AK2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AL2" t="s">
         <v>137</v>
@@ -3590,7 +3589,7 @@
         <v>106</v>
       </c>
       <c r="Q2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="R2" t="s">
         <v>137</v>
@@ -3603,7 +3602,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -3612,21 +3611,20 @@
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="10" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" customWidth="1"/>
-    <col min="16" max="16" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.85546875" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" customWidth="1"/>
+    <col min="15" max="15" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="10" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="10" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
@@ -3645,47 +3643,44 @@
       <c r="F1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="H1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>38</v>
       </c>
+      <c r="I1" s="15" t="s">
+        <v>61</v>
+      </c>
       <c r="J1" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="K1" s="15" t="s">
         <v>62</v>
       </c>
+      <c r="K1" s="14" t="s">
+        <v>56</v>
+      </c>
       <c r="L1" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="P1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="R1" s="11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -3704,47 +3699,44 @@
       <c r="F2" s="6">
         <v>0.02</v>
       </c>
-      <c r="G2" s="12" t="b">
+      <c r="G2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
+      <c r="I2" s="16">
+        <v>4</v>
       </c>
       <c r="J2" s="16">
-        <v>4</v>
-      </c>
-      <c r="K2" s="16">
         <v>20</v>
       </c>
+      <c r="K2" s="12">
+        <v>0</v>
+      </c>
       <c r="L2" s="12">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M2" s="12">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="N2" s="12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O2" s="12">
-        <v>10</v>
-      </c>
-      <c r="P2" s="12">
         <v>0.6</v>
       </c>
+      <c r="P2" t="s">
+        <v>52</v>
+      </c>
       <c r="Q2" t="s">
-        <v>52</v>
-      </c>
-      <c r="R2" t="s">
         <v>138</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -3763,43 +3755,40 @@
       <c r="F3" s="6">
         <v>0.02</v>
       </c>
-      <c r="G3" s="12" t="b">
+      <c r="G3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
+      <c r="I3" s="16">
+        <v>5</v>
       </c>
       <c r="J3" s="16">
+        <v>25</v>
+      </c>
+      <c r="K3" s="12">
+        <v>0</v>
+      </c>
+      <c r="L3" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="M3" s="12">
         <v>5</v>
       </c>
-      <c r="K3" s="16">
-        <v>25</v>
-      </c>
-      <c r="L3" s="12">
-        <v>0</v>
-      </c>
-      <c r="M3" s="12">
-        <v>0.5</v>
-      </c>
       <c r="N3" s="12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O3" s="12">
-        <v>10</v>
-      </c>
-      <c r="P3" s="12">
         <v>0.6</v>
       </c>
+      <c r="P3" t="s">
+        <v>70</v>
+      </c>
       <c r="Q3" t="s">
-        <v>70</v>
-      </c>
-      <c r="R3" t="s">
         <v>139</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>143</v>
       </c>
     </row>
@@ -3983,10 +3972,10 @@
         <v>8</v>
       </c>
       <c r="C1" s="51" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D1" s="52" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>40</v>
@@ -4001,7 +3990,7 @@
         <v>146</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J1" s="37" t="s">
         <v>147</v>
@@ -4061,10 +4050,10 @@
         <v>165</v>
       </c>
       <c r="AC1" s="41" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AD1" s="41" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AE1" s="41" t="s">
         <v>166</v>
@@ -4076,10 +4065,10 @@
         <v>168</v>
       </c>
       <c r="AH1" s="41" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AI1" s="18" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AJ1" s="41" t="s">
         <v>169</v>
@@ -4088,10 +4077,10 @@
         <v>170</v>
       </c>
       <c r="AL1" s="35" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM1" s="35" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AN1" s="35" t="s">
         <v>171</v>
@@ -4100,10 +4089,10 @@
         <v>172</v>
       </c>
       <c r="AP1" s="41" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AQ1" s="41" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AR1" s="41" t="s">
         <v>173</v>
@@ -4112,10 +4101,10 @@
         <v>174</v>
       </c>
       <c r="AT1" s="42" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AU1" s="42" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AV1" s="42" t="s">
         <v>175</v>
@@ -4124,10 +4113,10 @@
         <v>176</v>
       </c>
       <c r="AX1" s="35" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AY1" s="35" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AZ1" s="35" t="s">
         <v>177</v>
@@ -4174,13 +4163,13 @@
         <v>42</v>
       </c>
       <c r="J2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="K2">
         <v>0.7</v>
       </c>
       <c r="L2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="M2">
         <v>0.35</v>
